--- a/PHY-4B/labs/lab5/Delano Leslie - Lab 5 - Ohms Law Part 1.xlsx
+++ b/PHY-4B/labs/lab5/Delano Leslie - Lab 5 - Ohms Law Part 1.xlsx
@@ -101,16 +101,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">330</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve">330 </t>
     </r>
     <r>
       <rPr>
@@ -118,6 +109,7 @@
         <color theme="1"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Ω</t>
     </r>
@@ -137,16 +129,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">220</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve">220 </t>
     </r>
     <r>
       <rPr>
@@ -154,6 +137,7 @@
         <color theme="1"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Ω</t>
     </r>
@@ -173,16 +157,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">470</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
+      <t xml:space="preserve">470 </t>
     </r>
     <r>
       <rPr>
@@ -190,6 +165,7 @@
         <color theme="1"/>
         <rFont val="Times New Roman"/>
         <family val="1"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Ω</t>
     </r>
@@ -220,14 +196,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="5">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
     <numFmt numFmtId="166" formatCode="0.00"/>
     <numFmt numFmtId="167" formatCode="0.0"/>
-    <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -292,14 +267,9 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
@@ -310,34 +280,25 @@
     </font>
     <font>
       <sz val="13"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FFFF950E"/>
-      <name val="Arial"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF953CFE"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -474,172 +435,176 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="43">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="6" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -698,8 +663,8 @@
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
       <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF950E"/>
       <rgbColor rgb="FFFF9100"/>
+      <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF666699"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
@@ -734,6 +699,9 @@
             </a:pPr>
             <a:r>
               <a:rPr b="0" sz="1300" strike="noStrike" u="none">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
                 <a:uFillTx/>
                 <a:latin typeface="Arial"/>
               </a:rPr>
@@ -793,12 +761,16 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -965,12 +937,16 @@
                 <a:p>
                   <a:pPr>
                     <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                      <a:solidFill>
+                        <a:srgbClr val="000000"/>
+                      </a:solidFill>
                       <a:uFillTx/>
                       <a:latin typeface="Arial"/>
                     </a:defRPr>
                   </a:pPr>
                 </a:p>
               </c:txPr>
+              <c:dLblPos val="r"/>
               <c:showLegendKey val="0"/>
               <c:showVal val="0"/>
               <c:showCatName val="0"/>
@@ -984,12 +960,16 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -1127,7 +1107,7 @@
             </a:ln>
           </c:spPr>
           <c:marker>
-            <c:symbol val="star"/>
+            <c:symbol val="square"/>
             <c:size val="8"/>
             <c:spPr>
               <a:solidFill>
@@ -1142,12 +1122,16 @@
               <a:p>
                 <a:pPr>
                   <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:defRPr>
                 </a:pPr>
               </a:p>
             </c:txPr>
+            <c:dLblPos val="r"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="0"/>
             <c:showCatName val="0"/>
@@ -1262,11 +1246,11 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
-        <c:axId val="92821598"/>
-        <c:axId val="76113602"/>
+        <c:axId val="72148152"/>
+        <c:axId val="91061780"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="92821598"/>
+        <c:axId val="72148152"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1286,6 +1270,9 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr b="0" sz="900" strike="noStrike" u="none">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:rPr>
@@ -1302,7 +1289,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1319,18 +1306,21 @@
           <a:p>
             <a:pPr>
               <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
                 <a:uFillTx/>
                 <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="76113602"/>
+        <c:crossAx val="91061780"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="76113602"/>
+        <c:axId val="91061780"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1359,6 +1349,9 @@
                 </a:pPr>
                 <a:r>
                   <a:rPr b="0" sz="900" strike="noStrike" u="none">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
                     <a:uFillTx/>
                     <a:latin typeface="Arial"/>
                   </a:rPr>
@@ -1375,7 +1368,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00" sourceLinked="0"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1392,15 +1385,18 @@
           <a:p>
             <a:pPr>
               <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+                <a:solidFill>
+                  <a:srgbClr val="000000"/>
+                </a:solidFill>
                 <a:uFillTx/>
                 <a:latin typeface="Arial"/>
               </a:defRPr>
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92821598"/>
+        <c:crossAx val="72148152"/>
         <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
+        <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -1426,6 +1422,9 @@
         <a:p>
           <a:pPr>
             <a:defRPr b="0" sz="1000" strike="noStrike" u="none">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
               <a:uFillTx/>
               <a:latin typeface="Arial"/>
             </a:defRPr>
@@ -1458,9 +1457,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
-      <xdr:colOff>291960</xdr:colOff>
+      <xdr:colOff>291600</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>180000</xdr:rowOff>
+      <xdr:rowOff>179640</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -1469,7 +1468,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="6759720" y="4922280"/>
-        <a:ext cx="5759640" cy="3239640"/>
+        <a:ext cx="5759280" cy="3239280"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -1665,627 +1664,627 @@
   <dimension ref="C2:V31"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="14.25" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="4.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="2.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="2.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="2.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="2.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="2.73"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="2.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="3.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="10.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="3.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="18.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="3.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="6.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="5.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="3.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="0" width="12.82"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="0" width="3.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="0" width="3.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="0" width="2.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="1" width="2.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="2.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="2.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="2.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="2.73"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="2.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="3.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="10.18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="3.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="18.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="1" width="3.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="6.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="1" width="4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="1" width="5.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="1" width="3.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="25" min="25" style="1" width="12.82"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="26" style="1" width="3.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="27" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="28" min="28" style="1" width="3.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="30" min="30" style="1" width="2.27"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C2" s="1"/>
-      <c r="D2" s="2" t="s">
+      <c r="C2" s="2"/>
+      <c r="D2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="4"/>
-      <c r="N2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="5"/>
+      <c r="N2" s="5"/>
     </row>
     <row r="3" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C3" s="5"/>
-      <c r="D3" s="6" t="s">
+      <c r="C3" s="6"/>
+      <c r="D3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5"/>
     </row>
     <row r="4" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C4" s="8"/>
-      <c r="D4" s="9" t="s">
+      <c r="C4" s="9"/>
+      <c r="D4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="12" t="s">
+      <c r="F4" s="11"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="K4" s="13" t="s">
+      <c r="K4" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="L4" s="13"/>
-      <c r="M4" s="4"/>
-      <c r="N4" s="4"/>
+      <c r="L4" s="14"/>
+      <c r="M4" s="5"/>
+      <c r="N4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="16.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="6" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C6" s="1"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-      <c r="F6" s="14"/>
-      <c r="G6" s="14"/>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="15"/>
-      <c r="N6" s="16"/>
-      <c r="O6" s="16"/>
-      <c r="P6" s="16"/>
-      <c r="Q6" s="16"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+      <c r="G6" s="15"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="16"/>
+      <c r="N6" s="17"/>
+      <c r="O6" s="17"/>
+      <c r="P6" s="17"/>
+      <c r="Q6" s="17"/>
     </row>
     <row r="7" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C7" s="5"/>
-      <c r="D7" s="17" t="s">
+      <c r="C7" s="6"/>
+      <c r="D7" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="17"/>
-      <c r="H7" s="17"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="18"/>
-      <c r="L7" s="19"/>
-      <c r="M7" s="20"/>
-      <c r="N7" s="20"/>
-      <c r="O7" s="20"/>
-      <c r="P7" s="21"/>
-      <c r="Q7" s="21"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
+      <c r="J7" s="18"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="20"/>
+      <c r="M7" s="21"/>
+      <c r="N7" s="21"/>
+      <c r="O7" s="21"/>
+      <c r="P7" s="22"/>
+      <c r="Q7" s="22"/>
     </row>
     <row r="8" customFormat="false" ht="9.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C8" s="22"/>
-      <c r="D8" s="23"/>
-      <c r="E8" s="23"/>
-      <c r="F8" s="23"/>
-      <c r="G8" s="23"/>
-      <c r="K8" s="18"/>
-      <c r="L8" s="19"/>
-      <c r="M8" s="20"/>
-      <c r="N8" s="20"/>
-      <c r="O8" s="20"/>
-      <c r="P8" s="21"/>
-      <c r="Q8" s="21"/>
-      <c r="R8" s="24"/>
-      <c r="S8" s="24"/>
-      <c r="T8" s="24"/>
-      <c r="U8" s="24"/>
-      <c r="V8" s="24"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="20"/>
+      <c r="M8" s="21"/>
+      <c r="N8" s="21"/>
+      <c r="O8" s="21"/>
+      <c r="P8" s="22"/>
+      <c r="Q8" s="22"/>
+      <c r="R8" s="25"/>
+      <c r="S8" s="25"/>
+      <c r="T8" s="25"/>
+      <c r="U8" s="25"/>
+      <c r="V8" s="25"/>
     </row>
     <row r="9" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C9" s="25"/>
-      <c r="D9" s="26" t="s">
+      <c r="C9" s="26"/>
+      <c r="D9" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="27"/>
-      <c r="F9" s="26" t="s">
+      <c r="E9" s="28"/>
+      <c r="F9" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="G9" s="26"/>
-      <c r="H9" s="26"/>
-      <c r="J9" s="28" t="s">
+      <c r="G9" s="27"/>
+      <c r="H9" s="27"/>
+      <c r="J9" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="K9" s="18"/>
-      <c r="L9" s="19"/>
-      <c r="M9" s="20"/>
-      <c r="N9" s="20"/>
-      <c r="O9" s="20"/>
-      <c r="P9" s="21"/>
-      <c r="Q9" s="21"/>
-      <c r="R9" s="23"/>
-      <c r="S9" s="23"/>
+      <c r="K9" s="19"/>
+      <c r="L9" s="20"/>
+      <c r="M9" s="21"/>
+      <c r="N9" s="21"/>
+      <c r="O9" s="21"/>
+      <c r="P9" s="22"/>
+      <c r="Q9" s="22"/>
+      <c r="R9" s="24"/>
+      <c r="S9" s="24"/>
     </row>
     <row r="10" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C10" s="29"/>
-      <c r="D10" s="30" t="s">
+      <c r="C10" s="30"/>
+      <c r="D10" s="31" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="31"/>
-      <c r="F10" s="32" t="s">
+      <c r="E10" s="32"/>
+      <c r="F10" s="33" t="s">
         <v>13</v>
       </c>
-      <c r="G10" s="32"/>
-      <c r="H10" s="32"/>
-      <c r="J10" s="27" t="s">
+      <c r="G10" s="33"/>
+      <c r="H10" s="33"/>
+      <c r="J10" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="K10" s="18"/>
-      <c r="L10" s="19"/>
-      <c r="M10" s="20"/>
-      <c r="N10" s="20"/>
-      <c r="O10" s="20"/>
-      <c r="P10" s="21"/>
-      <c r="Q10" s="21"/>
-      <c r="R10" s="24"/>
-      <c r="S10" s="24"/>
-      <c r="T10" s="24"/>
-      <c r="V10" s="27"/>
+      <c r="K10" s="19"/>
+      <c r="L10" s="20"/>
+      <c r="M10" s="21"/>
+      <c r="N10" s="21"/>
+      <c r="O10" s="21"/>
+      <c r="P10" s="22"/>
+      <c r="Q10" s="22"/>
+      <c r="R10" s="25"/>
+      <c r="S10" s="25"/>
+      <c r="T10" s="25"/>
+      <c r="V10" s="28"/>
     </row>
     <row r="11" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C11" s="29"/>
-      <c r="D11" s="30" t="s">
+      <c r="C11" s="30"/>
+      <c r="D11" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="31"/>
-      <c r="F11" s="32" t="s">
+      <c r="E11" s="32"/>
+      <c r="F11" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="32"/>
-      <c r="H11" s="32"/>
-      <c r="J11" s="27" t="s">
+      <c r="G11" s="33"/>
+      <c r="H11" s="33"/>
+      <c r="J11" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="K11" s="18"/>
-      <c r="L11" s="19"/>
-      <c r="M11" s="20"/>
-      <c r="N11" s="20"/>
-      <c r="O11" s="20"/>
-      <c r="P11" s="21"/>
-      <c r="Q11" s="21"/>
-      <c r="R11" s="33"/>
-      <c r="S11" s="33"/>
-      <c r="T11" s="33"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="20"/>
+      <c r="M11" s="21"/>
+      <c r="N11" s="21"/>
+      <c r="O11" s="21"/>
+      <c r="P11" s="22"/>
+      <c r="Q11" s="22"/>
+      <c r="R11" s="34"/>
+      <c r="S11" s="34"/>
+      <c r="T11" s="34"/>
     </row>
     <row r="12" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C12" s="29"/>
-      <c r="D12" s="30" t="s">
+      <c r="C12" s="30"/>
+      <c r="D12" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="E12" s="31"/>
-      <c r="F12" s="32" t="s">
+      <c r="E12" s="32"/>
+      <c r="F12" s="33" t="s">
         <v>19</v>
       </c>
-      <c r="G12" s="32"/>
-      <c r="H12" s="32"/>
-      <c r="J12" s="27" t="s">
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
+      <c r="J12" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="K12" s="18"/>
-      <c r="L12" s="19"/>
-      <c r="M12" s="20"/>
-      <c r="N12" s="20"/>
-      <c r="O12" s="20"/>
-      <c r="P12" s="21"/>
-      <c r="Q12" s="21"/>
-      <c r="R12" s="33"/>
-      <c r="S12" s="33"/>
-      <c r="T12" s="33"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="20"/>
+      <c r="M12" s="21"/>
+      <c r="N12" s="21"/>
+      <c r="O12" s="21"/>
+      <c r="P12" s="22"/>
+      <c r="Q12" s="22"/>
+      <c r="R12" s="34"/>
+      <c r="S12" s="34"/>
+      <c r="T12" s="34"/>
     </row>
     <row r="13" customFormat="false" ht="10.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C13" s="8"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="34"/>
-      <c r="J13" s="34"/>
-      <c r="K13" s="35"/>
-      <c r="Q13" s="31"/>
-      <c r="R13" s="33"/>
-      <c r="S13" s="33"/>
-      <c r="T13" s="33"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="35"/>
+      <c r="E13" s="35"/>
+      <c r="F13" s="35"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="35"/>
+      <c r="J13" s="35"/>
+      <c r="K13" s="36"/>
+      <c r="Q13" s="32"/>
+      <c r="R13" s="34"/>
+      <c r="S13" s="34"/>
+      <c r="T13" s="34"/>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C15" s="1"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="14"/>
-      <c r="O15" s="15"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="15"/>
+      <c r="N15" s="15"/>
+      <c r="O15" s="16"/>
     </row>
     <row r="16" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C16" s="5"/>
-      <c r="D16" s="17" t="s">
+      <c r="C16" s="6"/>
+      <c r="D16" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
-      <c r="G16" s="17"/>
-      <c r="H16" s="17"/>
-      <c r="I16" s="17"/>
-      <c r="J16" s="17"/>
-      <c r="K16" s="17"/>
-      <c r="L16" s="17"/>
-      <c r="M16" s="17"/>
-      <c r="N16" s="17"/>
-      <c r="O16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="18"/>
+      <c r="J16" s="18"/>
+      <c r="K16" s="18"/>
+      <c r="L16" s="18"/>
+      <c r="M16" s="18"/>
+      <c r="N16" s="18"/>
+      <c r="O16" s="19"/>
     </row>
     <row r="17" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C17" s="5"/>
-      <c r="D17" s="36" t="s">
+      <c r="C17" s="6"/>
+      <c r="D17" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="E17" s="36"/>
-      <c r="F17" s="36"/>
-      <c r="G17" s="31"/>
-      <c r="H17" s="36" t="s">
+      <c r="E17" s="37"/>
+      <c r="F17" s="37"/>
+      <c r="G17" s="32"/>
+      <c r="H17" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="I17" s="36"/>
-      <c r="J17" s="36"/>
-      <c r="K17" s="31"/>
-      <c r="L17" s="36" t="s">
+      <c r="I17" s="37"/>
+      <c r="J17" s="37"/>
+      <c r="K17" s="32"/>
+      <c r="L17" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="M17" s="36"/>
-      <c r="N17" s="36"/>
-      <c r="O17" s="18"/>
+      <c r="M17" s="37"/>
+      <c r="N17" s="37"/>
+      <c r="O17" s="19"/>
     </row>
     <row r="18" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C18" s="5"/>
-      <c r="D18" s="37" t="s">
+      <c r="C18" s="6"/>
+      <c r="D18" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="E18" s="37"/>
-      <c r="F18" s="37"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="37" t="s">
+      <c r="E18" s="38"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="I18" s="37"/>
-      <c r="J18" s="37"/>
-      <c r="K18" s="31"/>
-      <c r="L18" s="37" t="s">
+      <c r="I18" s="38"/>
+      <c r="J18" s="38"/>
+      <c r="K18" s="32"/>
+      <c r="L18" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="M18" s="37"/>
-      <c r="N18" s="37"/>
-      <c r="O18" s="18"/>
+      <c r="M18" s="38"/>
+      <c r="N18" s="38"/>
+      <c r="O18" s="19"/>
     </row>
     <row r="19" customFormat="false" ht="8.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C19" s="5"/>
-      <c r="O19" s="18"/>
+      <c r="C19" s="6"/>
+      <c r="O19" s="19"/>
     </row>
     <row r="20" customFormat="false" ht="30.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C20" s="5"/>
-      <c r="D20" s="38" t="s">
+      <c r="C20" s="6"/>
+      <c r="D20" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="F20" s="38" t="s">
+      <c r="F20" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="G20" s="27"/>
-      <c r="H20" s="38" t="s">
+      <c r="G20" s="28"/>
+      <c r="H20" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="J20" s="38" t="s">
+      <c r="J20" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="L20" s="38" t="s">
+      <c r="L20" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="N20" s="38" t="s">
+      <c r="N20" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="O20" s="18"/>
+      <c r="O20" s="19"/>
     </row>
     <row r="21" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C21" s="5"/>
-      <c r="D21" s="39" t="n">
+      <c r="C21" s="6"/>
+      <c r="D21" s="40" t="n">
         <v>3.1</v>
       </c>
-      <c r="E21" s="40"/>
-      <c r="F21" s="39" t="n">
+      <c r="E21" s="41"/>
+      <c r="F21" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="H21" s="41" t="n">
+      <c r="H21" s="42" t="n">
         <v>4.5</v>
       </c>
-      <c r="I21" s="39"/>
-      <c r="J21" s="39" t="n">
+      <c r="I21" s="40"/>
+      <c r="J21" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="L21" s="39" t="n">
+      <c r="L21" s="40" t="n">
         <v>2.2</v>
       </c>
-      <c r="M21" s="39"/>
-      <c r="N21" s="39" t="n">
+      <c r="M21" s="40"/>
+      <c r="N21" s="40" t="n">
         <v>1</v>
       </c>
-      <c r="O21" s="18"/>
+      <c r="O21" s="19"/>
     </row>
     <row r="22" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C22" s="5"/>
-      <c r="D22" s="39" t="n">
+      <c r="C22" s="6"/>
+      <c r="D22" s="40" t="n">
         <v>6.1</v>
       </c>
-      <c r="E22" s="40"/>
-      <c r="F22" s="39" t="n">
+      <c r="E22" s="41"/>
+      <c r="F22" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="H22" s="41" t="n">
+      <c r="H22" s="42" t="n">
         <v>9.1</v>
       </c>
-      <c r="I22" s="39"/>
-      <c r="J22" s="39" t="n">
+      <c r="I22" s="40"/>
+      <c r="J22" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="L22" s="39" t="n">
+      <c r="L22" s="40" t="n">
         <v>4.3</v>
       </c>
-      <c r="M22" s="39"/>
-      <c r="N22" s="39" t="n">
+      <c r="M22" s="40"/>
+      <c r="N22" s="40" t="n">
         <v>2</v>
       </c>
-      <c r="O22" s="18"/>
+      <c r="O22" s="19"/>
     </row>
     <row r="23" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C23" s="5"/>
-      <c r="D23" s="39" t="n">
+      <c r="C23" s="6"/>
+      <c r="D23" s="40" t="n">
         <v>9.1</v>
       </c>
-      <c r="E23" s="40"/>
-      <c r="F23" s="39" t="n">
+      <c r="E23" s="41"/>
+      <c r="F23" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="H23" s="41" t="n">
+      <c r="H23" s="42" t="n">
         <v>13.6</v>
       </c>
-      <c r="I23" s="39"/>
-      <c r="J23" s="39" t="n">
+      <c r="I23" s="40"/>
+      <c r="J23" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="L23" s="39" t="n">
+      <c r="L23" s="40" t="n">
         <v>6.5</v>
       </c>
-      <c r="M23" s="39"/>
-      <c r="N23" s="39" t="n">
+      <c r="M23" s="40"/>
+      <c r="N23" s="40" t="n">
         <v>3</v>
       </c>
-      <c r="O23" s="18"/>
+      <c r="O23" s="19"/>
     </row>
     <row r="24" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C24" s="5"/>
-      <c r="D24" s="39" t="n">
+      <c r="C24" s="6"/>
+      <c r="D24" s="40" t="n">
         <v>12.3</v>
       </c>
-      <c r="E24" s="40"/>
-      <c r="F24" s="39" t="n">
+      <c r="E24" s="41"/>
+      <c r="F24" s="40" t="n">
         <v>4</v>
       </c>
-      <c r="H24" s="41" t="n">
+      <c r="H24" s="42" t="n">
         <v>18</v>
       </c>
-      <c r="I24" s="39"/>
-      <c r="J24" s="39" t="n">
+      <c r="I24" s="40"/>
+      <c r="J24" s="40" t="n">
         <v>4</v>
       </c>
-      <c r="L24" s="39" t="n">
+      <c r="L24" s="40" t="n">
         <v>8.6</v>
       </c>
-      <c r="M24" s="39"/>
-      <c r="N24" s="39" t="n">
+      <c r="M24" s="40"/>
+      <c r="N24" s="40" t="n">
         <v>4</v>
       </c>
-      <c r="O24" s="18"/>
+      <c r="O24" s="19"/>
     </row>
     <row r="25" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C25" s="5"/>
-      <c r="D25" s="39" t="n">
+      <c r="C25" s="6"/>
+      <c r="D25" s="40" t="n">
         <v>15.3</v>
       </c>
-      <c r="E25" s="40"/>
-      <c r="F25" s="39" t="n">
+      <c r="E25" s="41"/>
+      <c r="F25" s="40" t="n">
         <v>5</v>
       </c>
-      <c r="H25" s="41" t="n">
+      <c r="H25" s="42" t="n">
         <v>22.3</v>
       </c>
-      <c r="I25" s="39"/>
-      <c r="J25" s="39" t="n">
+      <c r="I25" s="40"/>
+      <c r="J25" s="40" t="n">
         <v>5</v>
       </c>
-      <c r="L25" s="39" t="n">
+      <c r="L25" s="40" t="n">
         <v>10.8</v>
       </c>
-      <c r="M25" s="39"/>
-      <c r="N25" s="39" t="n">
+      <c r="M25" s="40"/>
+      <c r="N25" s="40" t="n">
         <v>5</v>
       </c>
-      <c r="O25" s="18"/>
+      <c r="O25" s="19"/>
     </row>
     <row r="26" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C26" s="5"/>
-      <c r="D26" s="39" t="n">
+      <c r="C26" s="6"/>
+      <c r="D26" s="40" t="n">
         <v>18.5</v>
       </c>
-      <c r="E26" s="40"/>
-      <c r="F26" s="39" t="n">
+      <c r="E26" s="41"/>
+      <c r="F26" s="40" t="n">
         <v>6</v>
       </c>
-      <c r="H26" s="41" t="n">
+      <c r="H26" s="42" t="n">
         <v>27</v>
       </c>
-      <c r="I26" s="39"/>
-      <c r="J26" s="39" t="n">
+      <c r="I26" s="40"/>
+      <c r="J26" s="40" t="n">
         <v>6</v>
       </c>
-      <c r="L26" s="39" t="n">
+      <c r="L26" s="40" t="n">
         <v>13</v>
       </c>
-      <c r="M26" s="39"/>
-      <c r="N26" s="39" t="n">
+      <c r="M26" s="40"/>
+      <c r="N26" s="40" t="n">
         <v>6</v>
       </c>
-      <c r="O26" s="18"/>
+      <c r="O26" s="19"/>
     </row>
     <row r="27" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C27" s="5"/>
-      <c r="D27" s="39" t="n">
+      <c r="C27" s="6"/>
+      <c r="D27" s="40" t="n">
         <v>21.5</v>
       </c>
-      <c r="E27" s="40"/>
-      <c r="F27" s="39" t="n">
+      <c r="E27" s="41"/>
+      <c r="F27" s="40" t="n">
         <v>7</v>
       </c>
-      <c r="H27" s="41" t="n">
+      <c r="H27" s="42" t="n">
         <v>31.6</v>
       </c>
-      <c r="I27" s="39"/>
-      <c r="J27" s="39" t="n">
+      <c r="I27" s="40"/>
+      <c r="J27" s="40" t="n">
         <v>7</v>
       </c>
-      <c r="L27" s="39" t="n">
+      <c r="L27" s="40" t="n">
         <v>15.1</v>
       </c>
-      <c r="M27" s="39"/>
-      <c r="N27" s="39" t="n">
+      <c r="M27" s="40"/>
+      <c r="N27" s="40" t="n">
         <v>7</v>
       </c>
-      <c r="O27" s="18"/>
+      <c r="O27" s="19"/>
     </row>
     <row r="28" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C28" s="5"/>
-      <c r="D28" s="39" t="n">
+      <c r="C28" s="6"/>
+      <c r="D28" s="40" t="n">
         <v>24.7</v>
       </c>
-      <c r="E28" s="40"/>
-      <c r="F28" s="39" t="n">
+      <c r="E28" s="41"/>
+      <c r="F28" s="40" t="n">
         <v>8</v>
       </c>
-      <c r="H28" s="41" t="n">
+      <c r="H28" s="42" t="n">
         <v>36.3</v>
       </c>
-      <c r="I28" s="39"/>
-      <c r="J28" s="39" t="n">
+      <c r="I28" s="40"/>
+      <c r="J28" s="40" t="n">
         <v>8</v>
       </c>
-      <c r="L28" s="39" t="n">
+      <c r="L28" s="40" t="n">
         <v>17.3</v>
       </c>
-      <c r="M28" s="39"/>
-      <c r="N28" s="39" t="n">
+      <c r="M28" s="40"/>
+      <c r="N28" s="40" t="n">
         <v>8</v>
       </c>
-      <c r="O28" s="18"/>
+      <c r="O28" s="19"/>
     </row>
     <row r="29" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C29" s="5"/>
-      <c r="D29" s="39" t="n">
+      <c r="C29" s="6"/>
+      <c r="D29" s="40" t="n">
         <v>27.8</v>
       </c>
-      <c r="E29" s="40"/>
-      <c r="F29" s="39" t="n">
+      <c r="E29" s="41"/>
+      <c r="F29" s="40" t="n">
         <v>9</v>
       </c>
-      <c r="H29" s="41" t="n">
+      <c r="H29" s="42" t="n">
         <v>40.9</v>
       </c>
-      <c r="I29" s="39"/>
-      <c r="J29" s="39" t="n">
+      <c r="I29" s="40"/>
+      <c r="J29" s="40" t="n">
         <v>9</v>
       </c>
-      <c r="L29" s="39" t="n">
+      <c r="L29" s="40" t="n">
         <v>19.5</v>
       </c>
-      <c r="M29" s="39"/>
-      <c r="N29" s="39" t="n">
+      <c r="M29" s="40"/>
+      <c r="N29" s="40" t="n">
         <v>9</v>
       </c>
-      <c r="O29" s="18"/>
+      <c r="O29" s="19"/>
     </row>
     <row r="30" customFormat="false" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C30" s="5"/>
-      <c r="D30" s="39" t="n">
+      <c r="C30" s="6"/>
+      <c r="D30" s="40" t="n">
         <v>31</v>
       </c>
-      <c r="E30" s="40"/>
-      <c r="F30" s="39" t="n">
+      <c r="E30" s="41"/>
+      <c r="F30" s="40" t="n">
         <v>10</v>
       </c>
-      <c r="H30" s="41" t="n">
+      <c r="H30" s="42" t="n">
         <v>46.1</v>
       </c>
-      <c r="I30" s="39"/>
-      <c r="J30" s="39" t="n">
+      <c r="I30" s="40"/>
+      <c r="J30" s="40" t="n">
         <v>10</v>
       </c>
-      <c r="L30" s="39" t="n">
+      <c r="L30" s="40" t="n">
         <v>21.7</v>
       </c>
-      <c r="M30" s="39"/>
-      <c r="N30" s="39" t="n">
+      <c r="M30" s="40"/>
+      <c r="N30" s="40" t="n">
         <v>10</v>
       </c>
-      <c r="O30" s="18"/>
+      <c r="O30" s="19"/>
     </row>
     <row r="31" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="C31" s="8"/>
-      <c r="D31" s="34"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="34"/>
-      <c r="G31" s="34"/>
-      <c r="H31" s="34"/>
-      <c r="I31" s="34"/>
-      <c r="J31" s="34"/>
-      <c r="K31" s="34"/>
-      <c r="L31" s="34"/>
-      <c r="M31" s="34"/>
-      <c r="N31" s="34"/>
-      <c r="O31" s="35"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="35"/>
+      <c r="E31" s="35"/>
+      <c r="F31" s="35"/>
+      <c r="G31" s="35"/>
+      <c r="H31" s="35"/>
+      <c r="I31" s="35"/>
+      <c r="J31" s="35"/>
+      <c r="K31" s="35"/>
+      <c r="L31" s="35"/>
+      <c r="M31" s="35"/>
+      <c r="N31" s="35"/>
+      <c r="O31" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="16">
